--- a/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
@@ -1606,19 +1606,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1639,7 +1639,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1716,7 +1716,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1790,13 +1790,13 @@
         <v>30.82224430000005</v>
       </c>
       <c r="N4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="O4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="P4" t="n">
-        <v>5.790863699999997</v>
+        <v>5.790863699999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0285</v>
@@ -1808,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>26.28542482500007</v>
+        <v>26.28542482500006</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1846,22 +1846,22 @@
         <v>195.5</v>
       </c>
       <c r="F5" t="n">
-        <v>244.9923875000001</v>
+        <v>244.9923875</v>
       </c>
       <c r="G5" t="n">
-        <v>195.4999999999999</v>
+        <v>195.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8521474347826091</v>
+        <v>0.8521474347826088</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>42.50761249999988</v>
+        <v>42.50761249999996</v>
       </c>
       <c r="K5" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>30.82224430000005</v>
@@ -1873,7 +1873,7 @@
         <v>261.7714</v>
       </c>
       <c r="O5" t="n">
-        <v>216.7714000000001</v>
+        <v>216.7714</v>
       </c>
       <c r="P5" t="n">
         <v>2.6012568</v>
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="6">
@@ -1926,22 +1926,22 @@
         <v>241.5</v>
       </c>
       <c r="F6" t="n">
-        <v>298.9901408</v>
+        <v>298.9901408000001</v>
       </c>
       <c r="G6" t="n">
-        <v>241.5</v>
+        <v>241.4999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8124732086956522</v>
+        <v>0.8124732086956523</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>69.00985919999999</v>
+        <v>69.00985919999994</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>332.6215999999999</v>
+        <v>332.6216</v>
       </c>
       <c r="O6" t="n">
         <v>302.6216</v>
@@ -1959,7 +1959,7 @@
         <v>3.631459200000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01200000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="R6" t="n">
         <v>45.36986301369863</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-5.684341886080801e-14</v>
       </c>
     </row>
     <row r="7">
@@ -2006,19 +2006,19 @@
         <v>287.5</v>
       </c>
       <c r="F7" t="n">
-        <v>390.0000572000001</v>
+        <v>390.0000572</v>
       </c>
       <c r="G7" t="n">
         <v>287.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8695653449275365</v>
+        <v>0.8695653449275363</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>58.49994279999987</v>
+        <v>58.49994279999993</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>394.7369</v>
       </c>
       <c r="P7" t="n">
-        <v>4.736842799999999</v>
+        <v>4.7368428</v>
       </c>
       <c r="Q7" t="n">
         <v>0.012</v>
@@ -8667,10 +8667,10 @@
         <v>161.7714</v>
       </c>
       <c r="M18" t="n">
-        <v>161.7714000000001</v>
+        <v>161.7714</v>
       </c>
       <c r="N18" t="n">
-        <v>161.7714000000001</v>
+        <v>161.7714</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -10173,13 +10173,13 @@
         <v>2038</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8521474347826091</v>
+        <v>0.8521474347826088</v>
       </c>
       <c r="J2" t="n">
         <v>0.97</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1178525652173908</v>
+        <v>0.1178525652173912</v>
       </c>
     </row>
     <row r="3">
@@ -10212,13 +10212,13 @@
         <v>2039</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8124732086956522</v>
+        <v>0.8124732086956523</v>
       </c>
       <c r="J3" t="n">
         <v>0.97</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1575267913043478</v>
+        <v>0.1575267913043477</v>
       </c>
     </row>
     <row r="4">
@@ -10251,13 +10251,13 @@
         <v>2040</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8695653449275365</v>
+        <v>0.8695653449275363</v>
       </c>
       <c r="J4" t="n">
         <v>0.97</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1004346550724635</v>
+        <v>0.1004346550724636</v>
       </c>
     </row>
     <row r="5">
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0.99</v>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.99</v>
@@ -10752,7 +10752,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.8521474347826091</v>
+        <v>0.8521474347826088</v>
       </c>
       <c r="G11" t="n">
         <v>0.97</v>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.8124732086956522</v>
+        <v>0.8124732086956523</v>
       </c>
       <c r="G12" t="n">
         <v>0.97</v>
@@ -10977,7 +10977,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8695653449275365</v>
+        <v>0.8695653449275363</v>
       </c>
       <c r="G13" t="n">
         <v>0.97</v>
@@ -12096,7 +12096,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.01200000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="G36" t="n">
         <v>0.02</v>
@@ -22223,7 +22223,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>170.0174144999997</v>
+        <v>170.0174144999998</v>
       </c>
     </row>
     <row r="9">
@@ -22243,7 +22243,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="10">
@@ -22263,7 +22263,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.268484131370895</v>
+        <v>8.268484131370897</v>
       </c>
     </row>
     <row r="11">
@@ -22283,7 +22283,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.754764177838269</v>
+        <v>6.75476417783827</v>
       </c>
     </row>
     <row r="12">
@@ -22303,7 +22303,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.8124732086956522</v>
+        <v>0.8124732086956523</v>
       </c>
     </row>
     <row r="13">
@@ -22323,7 +22323,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9999999999999997</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -22403,7 +22403,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8703.159500000002</v>
+        <v>8703.1595</v>
       </c>
     </row>
     <row r="18">

--- a/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>3 / 3 / 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -821,7 +965,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -836,7 +980,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -854,7 +998,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -869,7 +1013,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -886,7 +1030,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,7 +1045,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -918,7 +1062,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -933,7 +1077,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -950,7 +1094,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -965,7 +1109,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -982,7 +1126,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -997,7 +1141,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1158,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1029,7 +1173,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1190,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1061,7 +1205,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1222,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1093,7 +1237,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1254,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1125,7 +1269,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1286,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1157,7 +1301,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1318,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1189,7 +1333,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1350,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1221,7 +1365,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1382,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1253,7 +1397,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1414,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1285,7 +1429,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1446,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1317,7 +1461,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1478,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1349,7 +1493,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1510,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1381,7 +1525,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1542,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1413,7 +1557,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1574,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1445,7 +1589,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10310,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2038: total service level 0.8521 &lt; 0.97 (shortage 42.508 t) [guideline in this scenario]</t>
+          <t>2038: общий уровень сервиса 0.8521 &lt; 0.97 (дефицит 42.508 т) [в этом сценарии — ориентир, не жёсткое ограничение]</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10205,7 +10349,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2039: total service level 0.8125 &lt; 0.97 (shortage 69.010 t) [guideline in this scenario]</t>
+          <t>2039: общий уровень сервиса 0.8125 &lt; 0.97 (дефицит 69.010 т) [в этом сценарии — ориентир, не жёсткое ограничение]</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10244,7 +10388,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2040: total service level 0.8696 &lt; 0.97 (shortage 58.500 t) [guideline in this scenario]</t>
+          <t>2040: общий уровень сервиса 0.8696 &lt; 0.97 (дефицит 58.500 т) [в этом сценарии — ориентир, не жёсткое ограничение]</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10283,7 +10427,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2038-01: physical stock 30.822 t &lt; 45-day reserve 35.445 t</t>
+          <t>2038-01: физический запас 30.822 т &lt; 45-дневного резерва 35.445 т</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -10325,7 +10469,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2039-01: physical stock 0.000 t &lt; 45-day reserve 45.370 t</t>
+          <t>2039-01: физический запас 0.000 т &lt; 45-дневного резерва 45.370 т</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -10367,7 +10511,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2040-01: physical stock 0.000 t &lt; 45-day reserve 55.295 t</t>
+          <t>2040-01: физический запас 0.000 т &lt; 45-дневного резерва 55.295 т</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -11764,7 +11908,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11777,7 +11921,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11813,7 +11957,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11826,7 +11970,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11862,7 +12006,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11875,7 +12019,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11911,7 +12055,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11924,7 +12068,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11960,7 +12104,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11973,7 +12117,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12153,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -12022,7 +12166,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12901,7 +13045,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -12911,7 +13055,7 @@
         <v/>
       </c>
       <c r="I53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -14170,7 +14314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M143"/>
+  <dimension ref="A1:N143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14239,6 +14383,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14294,6 +14443,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14349,6 +14503,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14404,6 +14563,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14459,6 +14623,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14514,6 +14683,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14569,6 +14743,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14624,6 +14803,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14679,6 +14863,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14734,6 +14923,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14789,6 +14983,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14844,6 +15043,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14899,6 +15103,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14954,6 +15163,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15009,6 +15223,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15064,6 +15283,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15119,6 +15343,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15174,6 +15403,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15229,6 +15463,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15284,6 +15523,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15339,6 +15583,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15394,6 +15643,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15449,6 +15703,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15504,6 +15763,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15559,6 +15823,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15614,6 +15883,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15654,11 +15928,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2035-01</t>
+          <t>2037-01</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -15667,7 +15941,12 @@
         </is>
       </c>
       <c r="M27" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -15724,6 +16003,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15764,11 +16048,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2035-02</t>
+          <t>2037-02</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -15777,7 +16061,12 @@
         </is>
       </c>
       <c r="M29" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -15834,6 +16123,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15874,11 +16168,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2035-03</t>
+          <t>2037-03</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -15887,7 +16181,12 @@
         </is>
       </c>
       <c r="M31" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -15944,6 +16243,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15984,11 +16288,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2035-04</t>
+          <t>2037-04</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -15997,7 +16301,12 @@
         </is>
       </c>
       <c r="M33" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -16054,6 +16363,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16094,11 +16408,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2035-05</t>
+          <t>2037-05</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -16107,7 +16421,12 @@
         </is>
       </c>
       <c r="M35" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -16164,6 +16483,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16204,11 +16528,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2035-06</t>
+          <t>2037-06</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -16217,7 +16541,12 @@
         </is>
       </c>
       <c r="M37" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -16274,6 +16603,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16314,11 +16648,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2035-07</t>
+          <t>2037-07</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -16327,7 +16661,12 @@
         </is>
       </c>
       <c r="M39" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -16384,6 +16723,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16424,11 +16768,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2037-08</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -16437,7 +16781,12 @@
         </is>
       </c>
       <c r="M41" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -16494,6 +16843,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16534,11 +16888,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2035-09</t>
+          <t>2037-09</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -16547,7 +16901,12 @@
         </is>
       </c>
       <c r="M43" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -16604,6 +16963,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16644,11 +17008,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2035-10</t>
+          <t>2037-10</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -16657,7 +17021,12 @@
         </is>
       </c>
       <c r="M45" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -16714,6 +17083,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16754,11 +17128,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2035-11</t>
+          <t>2037-11</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -16767,7 +17141,12 @@
         </is>
       </c>
       <c r="M47" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -16824,6 +17203,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16864,11 +17248,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2035-12</t>
+          <t>2037-12</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -16877,7 +17261,12 @@
         </is>
       </c>
       <c r="M49" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -16934,6 +17323,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16989,6 +17383,11 @@
       <c r="M51" t="b">
         <v>1</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -17044,6 +17443,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17099,6 +17503,11 @@
       <c r="M53" t="b">
         <v>1</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17154,6 +17563,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17209,6 +17623,11 @@
       <c r="M55" t="b">
         <v>1</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17264,6 +17683,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17319,6 +17743,11 @@
       <c r="M57" t="b">
         <v>1</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17374,6 +17803,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17429,6 +17863,11 @@
       <c r="M59" t="b">
         <v>1</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17484,6 +17923,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17539,6 +17983,11 @@
       <c r="M61" t="b">
         <v>1</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -17594,6 +18043,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17649,6 +18103,11 @@
       <c r="M63" t="b">
         <v>1</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17704,6 +18163,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17759,6 +18223,11 @@
       <c r="M65" t="b">
         <v>1</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17814,6 +18283,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17869,6 +18343,11 @@
       <c r="M67" t="b">
         <v>1</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17924,6 +18403,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17979,6 +18463,11 @@
       <c r="M69" t="b">
         <v>1</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18034,6 +18523,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18089,6 +18583,11 @@
       <c r="M71" t="b">
         <v>1</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18144,6 +18643,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18184,20 +18688,25 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t>2039-01</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t>2037-01</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>2037-01</t>
-        </is>
-      </c>
       <c r="M73" t="b">
         <v>1</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -18254,6 +18763,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18309,6 +18823,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18349,11 +18868,11 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J76" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2037-02</t>
+          <t>2039-02</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -18363,6 +18882,11 @@
       </c>
       <c r="M76" t="b">
         <v>1</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -18419,6 +18943,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18474,6 +19003,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18514,11 +19048,11 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J79" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2037-03</t>
+          <t>2039-03</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -18528,6 +19062,11 @@
       </c>
       <c r="M79" t="b">
         <v>1</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -18584,6 +19123,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18639,6 +19183,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18679,11 +19228,11 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J82" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2037-04</t>
+          <t>2039-04</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -18693,6 +19242,11 @@
       </c>
       <c r="M82" t="b">
         <v>1</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -18749,6 +19303,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18804,6 +19363,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18844,11 +19408,11 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J85" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2037-05</t>
+          <t>2039-05</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -18858,6 +19422,11 @@
       </c>
       <c r="M85" t="b">
         <v>1</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -18914,6 +19483,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -18969,6 +19543,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -19009,11 +19588,11 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J88" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2037-06</t>
+          <t>2039-06</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -19023,6 +19602,11 @@
       </c>
       <c r="M88" t="b">
         <v>1</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -19079,6 +19663,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -19134,6 +19723,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -19174,11 +19768,11 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J91" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2037-07</t>
+          <t>2039-07</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -19188,6 +19782,11 @@
       </c>
       <c r="M91" t="b">
         <v>1</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -19244,6 +19843,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19299,6 +19903,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19339,11 +19948,11 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J94" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2039-08</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -19353,6 +19962,11 @@
       </c>
       <c r="M94" t="b">
         <v>1</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -19409,6 +20023,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19464,6 +20083,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19504,11 +20128,11 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J97" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2037-09</t>
+          <t>2039-09</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -19518,6 +20142,11 @@
       </c>
       <c r="M97" t="b">
         <v>1</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -19574,6 +20203,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -19629,6 +20263,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19669,11 +20308,11 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J100" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2037-10</t>
+          <t>2039-10</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -19683,6 +20322,11 @@
       </c>
       <c r="M100" t="b">
         <v>1</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -19739,6 +20383,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19794,6 +20443,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19834,11 +20488,11 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J103" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2037-11</t>
+          <t>2039-11</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -19848,6 +20502,11 @@
       </c>
       <c r="M103" t="b">
         <v>1</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -19904,6 +20563,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19959,6 +20623,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19999,11 +20668,11 @@
         <v>1.885133333333333</v>
       </c>
       <c r="J106" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2037-12</t>
+          <t>2039-12</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -20013,6 +20682,11 @@
       </c>
       <c r="M106" t="b">
         <v>1</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -20069,6 +20743,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20124,6 +20803,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20164,11 +20848,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J109" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2038-01</t>
+          <t>2040-01</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -20178,6 +20862,11 @@
       </c>
       <c r="M109" t="b">
         <v>1</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -20234,6 +20923,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20289,6 +20983,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -20329,11 +21028,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J112" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2038-02</t>
+          <t>2040-02</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -20343,6 +21042,11 @@
       </c>
       <c r="M112" t="b">
         <v>1</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -20399,6 +21103,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -20454,6 +21163,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20494,11 +21208,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J115" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2038-03</t>
+          <t>2040-03</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -20508,6 +21222,11 @@
       </c>
       <c r="M115" t="b">
         <v>1</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -20564,6 +21283,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20619,6 +21343,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20659,11 +21388,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J118" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2038-04</t>
+          <t>2040-04</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -20673,6 +21402,11 @@
       </c>
       <c r="M118" t="b">
         <v>1</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -20729,6 +21463,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20784,6 +21523,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20824,11 +21568,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J121" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2038-05</t>
+          <t>2040-05</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -20838,6 +21582,11 @@
       </c>
       <c r="M121" t="b">
         <v>1</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -20894,6 +21643,11 @@
       <c r="M122" t="b">
         <v>1</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20949,6 +21703,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20989,11 +21748,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J124" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2038-06</t>
+          <t>2040-06</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -21003,6 +21762,11 @@
       </c>
       <c r="M124" t="b">
         <v>1</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -21059,6 +21823,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -21114,6 +21883,11 @@
       <c r="M126" t="b">
         <v>1</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -21154,11 +21928,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J127" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2038-07</t>
+          <t>2040-07</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -21168,6 +21942,11 @@
       </c>
       <c r="M127" t="b">
         <v>1</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -21224,6 +22003,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21279,6 +22063,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -21319,11 +22108,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J130" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2040-08</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -21333,6 +22122,11 @@
       </c>
       <c r="M130" t="b">
         <v>1</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -21389,6 +22183,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21444,6 +22243,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21484,11 +22288,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J133" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2038-09</t>
+          <t>2040-09</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -21498,6 +22302,11 @@
       </c>
       <c r="M133" t="b">
         <v>1</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -21554,6 +22363,11 @@
       <c r="M134" t="b">
         <v>1</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21609,6 +22423,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21649,11 +22468,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J136" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2038-10</t>
+          <t>2040-10</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -21663,6 +22482,11 @@
       </c>
       <c r="M136" t="b">
         <v>1</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -21719,6 +22543,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21774,6 +22603,11 @@
       <c r="M138" t="b">
         <v>1</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -21814,11 +22648,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J139" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2038-11</t>
+          <t>2040-11</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -21828,6 +22662,11 @@
       </c>
       <c r="M139" t="b">
         <v>1</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -21884,6 +22723,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -21939,6 +22783,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -21979,11 +22828,11 @@
         <v>7.061408333333334</v>
       </c>
       <c r="J142" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2038-12</t>
+          <t>2040-12</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -21993,6 +22842,11 @@
       </c>
       <c r="M142" t="b">
         <v>1</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -22048,6 +22902,11 @@
       </c>
       <c r="M143" t="b">
         <v>1</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -22643,7 +23502,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1590,6 +1590,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -11897,18 +11930,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11921,7 +11954,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11946,18 +11979,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11970,7 +12003,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11995,18 +12028,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -12019,7 +12052,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12044,18 +12077,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -12068,7 +12101,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12093,18 +12126,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -12117,7 +12150,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12142,18 +12175,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -12166,7 +12199,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12359,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -12350,7 +12383,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12561,7 +12594,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -12585,7 +12618,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12796,11 +12829,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>30.82224430000005</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G48" t="n">
         <v>70</v>
@@ -12820,7 +12853,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13162,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -13153,7 +13186,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13495,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -13486,7 +13519,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13893,7 +13926,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -13917,7 +13950,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,6 +1622,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
@@ -7585,7 +7585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7694,6 +7694,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7769,6 +7774,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7844,6 +7852,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7919,6 +7930,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7994,6 +8008,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8069,6 +8086,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8144,6 +8164,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8219,6 +8242,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8294,6 +8320,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8369,6 +8398,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8444,6 +8476,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8519,6 +8554,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8594,6 +8632,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8669,6 +8710,9 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8744,6 +8788,9 @@
       <c r="U15" t="n">
         <v>3.9567</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8819,6 +8866,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8894,6 +8944,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8969,6 +9022,9 @@
       <c r="U18" t="n">
         <v>72.7974</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9044,6 +9100,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9119,6 +9178,9 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9194,6 +9256,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9269,6 +9334,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9344,6 +9412,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9419,6 +9490,9 @@
       <c r="U24" t="n">
         <v>0</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9494,6 +9568,9 @@
       <c r="U25" t="n">
         <v>6.7866</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9569,6 +9646,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9644,6 +9724,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9719,6 +9802,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9794,6 +9880,9 @@
       <c r="U29" t="n">
         <v>0</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9869,6 +9958,9 @@
       <c r="U30" t="n">
         <v>25.4211</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9944,6 +10036,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10017,6 +10112,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10031,7 +10129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10095,6 +10193,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10137,6 +10240,9 @@
       <c r="L2" t="n">
         <v>360</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10179,6 +10285,9 @@
       <c r="L3" t="n">
         <v>1610</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10221,6 +10330,9 @@
       <c r="L4" t="n">
         <v>1790</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10263,6 +10375,9 @@
       <c r="L5" t="n">
         <v>1790</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10305,6 +10420,9 @@
       <c r="L6" t="n">
         <v>1790</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10346,6 +10464,9 @@
       </c>
       <c r="L7" t="n">
         <v>1790</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23052,7 +23173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23490,11 +23611,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -23510,11 +23631,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -23530,11 +23651,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -23550,7 +23671,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -23570,11 +23691,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -23590,10 +23711,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23610,11 +23731,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>78</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -23630,10 +23751,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>72</v>
       </c>
     </row>

--- a/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P4_full_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -917,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1441,7 +1443,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1461,24 +1463,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1488,29 +1490,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1520,29 +1522,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1552,176 +1554,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2458,6 +2603,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2530,6 +2685,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2601,6 +2762,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2672,6 +2839,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2743,6 +2916,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2814,6 +2993,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2885,6 +3070,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2956,6 +3147,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3027,6 +3224,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3098,6 +3301,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3169,6 +3378,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3240,6 +3455,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3311,6 +3532,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3382,6 +3609,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3453,6 +3686,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3524,6 +3763,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3595,6 +3840,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3666,6 +3917,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3737,6 +3994,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3808,6 +4071,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3879,6 +4148,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3950,6 +4225,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4021,6 +4302,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4092,6 +4379,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4163,6 +4456,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4234,6 +4533,12 @@
         <v>1.415606307500004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.59530225000007</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4305,6 +4610,12 @@
         <v>1.435829962500004</v>
       </c>
       <c r="U27" t="n">
+        <v>39.93236316666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4376,6 +4687,12 @@
         <v>1.456053617500004</v>
       </c>
       <c r="U28" t="n">
+        <v>40.2694240833334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4447,6 +4764,12 @@
         <v>1.476277272500004</v>
       </c>
       <c r="U29" t="n">
+        <v>40.60648500000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4518,6 +4841,12 @@
         <v>1.496500927500004</v>
       </c>
       <c r="U30" t="n">
+        <v>40.94354591666674</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4589,6 +4918,12 @@
         <v>1.516724582500004</v>
       </c>
       <c r="U31" t="n">
+        <v>41.2806068333334</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4660,6 +4995,12 @@
         <v>1.553711264000004</v>
       </c>
       <c r="U32" t="n">
+        <v>42.17643530000007</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4731,6 +5072,12 @@
         <v>1.607460972000004</v>
       </c>
       <c r="U33" t="n">
+        <v>43.07226376666673</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4802,6 +5149,12 @@
         <v>1.661210680000003</v>
       </c>
       <c r="U34" t="n">
+        <v>43.96809223333339</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4873,6 +5226,12 @@
         <v>1.714960388000003</v>
       </c>
       <c r="U35" t="n">
+        <v>44.86392070000006</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4944,6 +5303,12 @@
         <v>1.768710096000003</v>
       </c>
       <c r="U36" t="n">
+        <v>45.75974916666672</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5015,6 +5380,12 @@
         <v>1.822459804000003</v>
       </c>
       <c r="U37" t="n">
+        <v>46.65557763333339</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5086,6 +5457,12 @@
         <v>1.530160016000003</v>
       </c>
       <c r="U38" t="n">
+        <v>44.14142290000005</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5157,6 +5534,12 @@
         <v>0.8918107320000032</v>
       </c>
       <c r="U39" t="n">
+        <v>33.50226816666672</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5228,6 +5611,12 @@
         <v>0.416481448000003</v>
       </c>
       <c r="U40" t="n">
+        <v>28.29711343333338</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5299,6 +5688,12 @@
         <v>0.1301634030000015</v>
       </c>
       <c r="U41" t="n">
+        <v>23.09195870000005</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5370,6 +5765,12 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5441,6 +5842,12 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5512,6 +5919,12 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5583,6 +5996,12 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5654,6 +6073,12 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5725,6 +6150,12 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5796,6 +6227,12 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5867,6 +6304,12 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5938,6 +6381,12 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6009,6 +6458,12 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6080,6 +6535,12 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6151,6 +6612,12 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6222,6 +6689,12 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6293,6 +6766,12 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6364,6 +6843,12 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6435,6 +6920,12 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6506,6 +6997,12 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6577,6 +7074,12 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6648,6 +7151,12 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6719,6 +7228,12 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6790,6 +7305,12 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6861,6 +7382,12 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6932,6 +7459,12 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7003,6 +7536,12 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7074,6 +7613,12 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7145,6 +7690,12 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7216,6 +7767,12 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7287,6 +7844,12 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7358,6 +7921,12 @@
         <v>0</v>
       </c>
       <c r="U70" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7429,6 +7998,12 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7500,6 +8075,12 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7571,6 +8152,12 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10220,7 +10807,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10229,13 +10816,13 @@
         <v>360</v>
       </c>
       <c r="I2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="L2" t="n">
         <v>360</v>
@@ -10794,7 +11381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12620,7 +13207,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12628,14 +13215,14 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G39" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -12652,7 +13239,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12669,7 +13256,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -12677,14 +13264,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>109.876</v>
       </c>
       <c r="G40" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -12718,7 +13305,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12726,18 +13313,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I41" t="b">
         <v>1</v>
@@ -12747,7 +13335,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12762,7 +13354,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12770,7 +13362,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -12806,27 +13398,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -12836,11 +13427,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12855,7 +13442,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -12863,14 +13450,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G44" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -12887,7 +13474,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12904,7 +13491,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -12912,14 +13499,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G45" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -12936,7 +13523,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12953,7 +13540,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -12961,170 +13548,170 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G46" t="n">
+        <v>190</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G47" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46">
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48">
         <f>=</f>
         <v/>
       </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D49" t="n">
         <v>2036</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47">
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <f>=</f>
         <v/>
       </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>25.44727350000007</v>
-      </c>
-      <c r="G48" t="n">
-        <v>70</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>190</v>
-      </c>
-      <c r="G49" t="n">
-        <v>190</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13139,7 +13726,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -13147,14 +13734,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>190</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G50" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -13171,7 +13758,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13775,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -13196,14 +13783,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>13.189</v>
+        <v>41.2806068333334</v>
       </c>
       <c r="G51" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -13220,7 +13807,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13237,7 +13824,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -13245,14 +13832,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>13.1882</v>
+        <v>190</v>
       </c>
       <c r="G52" t="n">
-        <v>13.189</v>
+        <v>190</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -13269,7 +13856,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13873,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -13294,219 +13881,219 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>190</v>
+      </c>
+      <c r="G53" t="n">
+        <v>190</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="G54" t="n">
+        <v>130</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>13.1882</v>
+      </c>
+      <c r="G55" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53">
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56">
         <f>=</f>
         <v/>
       </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D57" t="n">
         <v>2037</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54">
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57">
         <f>=</f>
         <v/>
       </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>20.18308956666672</v>
-      </c>
-      <c r="G55" t="n">
-        <v>120</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2038-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="G56" t="n">
-        <v>190</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>161.7714</v>
-      </c>
-      <c r="G57" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13521,7 +14108,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -13529,11 +14116,11 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>120</v>
+        <v>20.18308956666672</v>
       </c>
       <c r="G58" t="n">
         <v>120</v>
@@ -13553,7 +14140,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13570,7 +14157,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -13578,14 +14165,14 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>44.14142290000005</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -13602,7 +14189,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13619,7 +14206,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -13627,268 +14214,268 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="G60" t="n">
+        <v>190</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>161.7714</v>
+      </c>
+      <c r="G61" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>120</v>
+      </c>
+      <c r="G62" t="n">
+        <v>120</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>100</v>
+      </c>
+      <c r="G63" t="n">
+        <v>100</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60">
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64">
         <f>=</f>
         <v/>
       </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D65" t="n">
         <v>2038</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61">
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65">
         <f>=</f>
         <v/>
       </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>120</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2039-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>190</v>
-      </c>
-      <c r="G63" t="n">
-        <v>190</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>190</v>
-      </c>
-      <c r="G64" t="n">
-        <v>190</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>reserved_C_t_per_year</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>22.622</v>
-      </c>
-      <c r="G65" t="n">
-        <v>130</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Earth-New</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -13903,7 +14490,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -13911,14 +14498,14 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>22.6216</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>22.622</v>
+        <v>120</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -13935,7 +14522,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2039-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13952,7 +14539,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -13960,11 +14547,11 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>120</v>
+        <v>24.91584506666667</v>
       </c>
       <c r="G67" t="n">
         <v>120</v>
@@ -13984,7 +14571,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2039-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14001,7 +14588,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -14009,14 +14596,14 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G68" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -14033,7 +14620,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14637,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -14058,317 +14645,317 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>190</v>
+      </c>
+      <c r="G69" t="n">
+        <v>190</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>22.622</v>
+      </c>
+      <c r="G70" t="n">
+        <v>130</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>22.6216</v>
+      </c>
+      <c r="G71" t="n">
+        <v>22.622</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>120</v>
+      </c>
+      <c r="G72" t="n">
+        <v>120</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>120</v>
+      </c>
+      <c r="G73" t="n">
+        <v>120</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69">
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74">
         <f>=</f>
         <v/>
       </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D75" t="n">
         <v>2039</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70">
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75">
         <f>=</f>
         <v/>
       </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>120</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>2040-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>190</v>
-      </c>
-      <c r="G72" t="n">
-        <v>190</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>190</v>
-      </c>
-      <c r="G73" t="n">
-        <v>190</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>reserved_C_t_per_year</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>84.73699999999999</v>
-      </c>
-      <c r="G74" t="n">
-        <v>130</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Earth-New</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ordered_C_t</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>84.73690000000001</v>
-      </c>
-      <c r="G75" t="n">
-        <v>84.73699999999999</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Earth-New</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -14383,7 +14970,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -14391,11 +14978,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>120</v>
@@ -14415,7 +15002,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14432,7 +15019,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -14440,11 +15027,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>120</v>
+        <v>32.50000476666667</v>
       </c>
       <c r="G77" t="n">
         <v>120</v>
@@ -14464,7 +15051,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14481,7 +15068,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -14489,72 +15076,366 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>190</v>
+      </c>
+      <c r="G78" t="n">
+        <v>190</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>190</v>
+      </c>
+      <c r="G79" t="n">
+        <v>190</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>84.73699999999999</v>
+      </c>
+      <c r="G80" t="n">
+        <v>130</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>84.73690000000001</v>
+      </c>
+      <c r="G81" t="n">
+        <v>84.73699999999999</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>120</v>
+      </c>
+      <c r="G82" t="n">
+        <v>120</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>120</v>
+      </c>
+      <c r="G83" t="n">
+        <v>120</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78">
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84">
         <f>=</f>
         <v/>
       </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D85" t="n">
         <v>2040</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79">
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85">
         <f>=</f>
         <v/>
       </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23173,7 +24054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23215,7 +24096,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11278.068363673</v>
+        <v>11278.438229443</v>
       </c>
     </row>
     <row r="3">
@@ -23235,7 +24116,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9213.380707730626</v>
+        <v>9213.750573500627</v>
       </c>
     </row>
     <row r="4">
@@ -23375,7 +24256,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.268484131370897</v>
+        <v>8.268755297420913</v>
       </c>
     </row>
     <row r="11">
@@ -23395,7 +24276,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.75476417783827</v>
+        <v>6.755035343888286</v>
       </c>
     </row>
     <row r="12">
@@ -23555,7 +24436,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47.19299367300009</v>
+        <v>47.56285944300009</v>
       </c>
     </row>
     <row r="20">
@@ -23671,11 +24552,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -23691,11 +24572,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -23711,11 +24592,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -23731,11 +24612,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -23751,11 +24632,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -23771,11 +24652,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>72</v>
+      <c r="D32" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
